--- a/backend/data/frequency_analysis.xlsx
+++ b/backend/data/frequency_analysis.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,71 +425,42 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>&lt;표 4-1&gt; 조사대상자의 일반적 특성</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B3" s="1" t="inlineStr">
         <is>
           <t>범주</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>빈도(N)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D3" s="1" t="inlineStr">
         <is>
           <t>비율(%)</t>
         </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>성별</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>93</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.8</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>성별</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>199</v>
-      </c>
-      <c r="D3" t="n">
-        <v>68.2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>연령</t>
+          <t>귀하의 연령은?</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -498,16 +469,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>8.199999999999999</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>연령</t>
+          <t>귀하의 연령은?</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -516,16 +487,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>34</v>
+        <v>146</v>
       </c>
       <c r="D5" t="n">
-        <v>11.6</v>
+        <v>35.3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>연령</t>
+          <t>귀하의 연령은?</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -534,16 +505,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>50</v>
+        <v>184</v>
       </c>
       <c r="D6" t="n">
-        <v>17.1</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>연령</t>
+          <t>귀하의 연령은?</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -552,34 +523,34 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="D7" t="n">
-        <v>39</v>
+        <v>19.1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>연령</t>
+          <t>귀하의 학력은?</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>학력</t>
+          <t>귀하의 학력은?</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -588,16 +559,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>88</v>
+        <v>130</v>
       </c>
       <c r="D9" t="n">
-        <v>30.1</v>
+        <v>31.4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>학력</t>
+          <t>귀하의 학력은?</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -606,16 +577,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>130</v>
+        <v>220</v>
       </c>
       <c r="D10" t="n">
-        <v>44.5</v>
+        <v>53.1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>학력</t>
+          <t>귀하의 학력은?</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -624,16 +595,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="D11" t="n">
-        <v>25.3</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>월평균소득</t>
+          <t>귀하의 직업은? (복수로 체크 가능)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -642,268 +613,268 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>67</v>
+        <v>143</v>
       </c>
       <c r="D12" t="n">
-        <v>22.9</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>월평균소득</t>
+          <t>귀하의 직업은? (복수로 체크 가능)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1, 4</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>41.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>월평균소득</t>
+          <t>귀하의 직업은? (복수로 체크 가능)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="D14" t="n">
-        <v>19.9</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>월평균소득</t>
+          <t>귀하의 직업은? (복수로 체크 가능)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="D15" t="n">
-        <v>16.1</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>재직기간</t>
+          <t>귀하의 직업은? (복수로 체크 가능)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>31</v>
+        <v>85</v>
       </c>
       <c r="D16" t="n">
-        <v>10.6</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>재직기간</t>
+          <t>귀하의 직업은? (복수로 체크 가능)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>26</v>
+        <v>78</v>
       </c>
       <c r="D17" t="n">
-        <v>8.9</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>재직기간</t>
+          <t>귀하의 직업은? (복수로 체크 가능)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="D18" t="n">
-        <v>10.3</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>재직기간</t>
+          <t>귀하의 월소득 수준은?</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>57</v>
+        <v>182</v>
       </c>
       <c r="D19" t="n">
-        <v>19.5</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>재직기간</t>
+          <t>귀하의 월소득 수준은?</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>85</v>
+        <v>161</v>
       </c>
       <c r="D20" t="n">
-        <v>29.1</v>
+        <v>38.9</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>재직기간</t>
+          <t>귀하의 월소득 수준은?</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D21" t="n">
-        <v>21.6</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>직위</t>
+          <t>귀하의 월소득 수준은?</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="D22" t="n">
-        <v>8.9</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>직위</t>
+          <t>귀하가 거주하는 지역은 ?</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>35</v>
+        <v>181</v>
       </c>
       <c r="D23" t="n">
-        <v>12</v>
+        <v>43.7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>직위</t>
+          <t>귀하가 거주하는 지역은 ?</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>50</v>
+        <v>205</v>
       </c>
       <c r="D24" t="n">
-        <v>17.1</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>직위</t>
+          <t>귀하가 거주하는 지역은 ?</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>153</v>
+        <v>12</v>
       </c>
       <c r="D25" t="n">
-        <v>52.4</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>직위</t>
+          <t>귀하가 거주하는 지역은 ?</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="D26" t="n">
-        <v>9.6</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>전문분야</t>
+          <t>귀하의 종교는 ?</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -912,16 +883,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>206</v>
+        <v>401</v>
       </c>
       <c r="D27" t="n">
-        <v>70.5</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>전문분야</t>
+          <t>귀하의 종교는 ?</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -930,60 +901,247 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>86</v>
+        <v>3</v>
       </c>
       <c r="D28" t="n">
-        <v>29.5</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>고용형태</t>
+          <t>귀하의 종교는 ?</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>102</v>
+        <v>2</v>
       </c>
       <c r="D29" t="n">
-        <v>34.9</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>고용형태</t>
+          <t>귀하의 종교는 ?</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>190</v>
+        <v>8</v>
       </c>
       <c r="D30" t="n">
-        <v>65.09999999999999</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>귀하의 성경 통독 횟수는 ?</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>72</v>
+      </c>
+      <c r="D31" t="n">
+        <v>17.4</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>귀하의 성경 통독 횟수는 ?</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>68</v>
+      </c>
+      <c r="D32" t="n">
+        <v>16.4</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>귀하의 성경 통독 횟수는 ?</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>191</v>
+      </c>
+      <c r="D33" t="n">
+        <v>46.1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>귀하의 성경 통독 횟수는 ?</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>83</v>
+      </c>
+      <c r="D34" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>귀하의 교회 직분은 무엇입니까?</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>185</v>
+      </c>
+      <c r="D35" t="n">
+        <v>44.7</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>귀하의 교회 직분은 무엇입니까?</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>167</v>
+      </c>
+      <c r="D36" t="n">
+        <v>40.3</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>귀하의 교회 직분은 무엇입니까?</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>47</v>
+      </c>
+      <c r="D37" t="n">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>귀하의 교회 직분은 무엇입니까?</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>15</v>
+      </c>
+      <c r="D38" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>성별</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>128</v>
+      </c>
+      <c r="D39" t="n">
+        <v>30.9</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>성별</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>286</v>
+      </c>
+      <c r="D40" t="n">
+        <v>69.09999999999999</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="n">
-        <v>292</v>
-      </c>
-      <c r="D31" t="n">
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="n">
+        <v>414</v>
+      </c>
+      <c r="D41" t="n">
         <v>100</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>총 유효 표본(N) = 414명</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/backend/data/frequency_analysis.xlsx
+++ b/backend/data/frequency_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,349 +460,349 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>귀하의 연령은?</t>
+          <t>귀하의연령은</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>151</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>귀하의 연령은?</t>
+          <t>귀하의연령은</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>146</v>
+        <v>184</v>
       </c>
       <c r="D5" t="n">
-        <v>35.3</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>귀하의 연령은?</t>
+          <t>귀하의연령은</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>184</v>
+        <v>79</v>
       </c>
       <c r="D6" t="n">
-        <v>44.4</v>
+        <v>19.1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>귀하의 연령은?</t>
+          <t>귀하의학력은</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>79</v>
+        <v>134</v>
       </c>
       <c r="D7" t="n">
-        <v>19.1</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>귀하의 학력은?</t>
+          <t>귀하의학력은</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>220</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>53.1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>귀하의 학력은?</t>
+          <t>귀하의학력은</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="D9" t="n">
-        <v>31.4</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>귀하의 학력은?</t>
+          <t>귀하의직업은복수로체크가능</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>220</v>
+        <v>143</v>
       </c>
       <c r="D10" t="n">
-        <v>53.1</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>귀하의 학력은?</t>
+          <t>귀하의직업은복수로체크가능</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D11" t="n">
-        <v>14.5</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>귀하의 직업은? (복수로 체크 가능)</t>
+          <t>귀하의직업은복수로체크가능</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>143</v>
+        <v>23</v>
       </c>
       <c r="D12" t="n">
-        <v>34.5</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>귀하의 직업은? (복수로 체크 가능)</t>
+          <t>귀하의직업은복수로체크가능</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1, 4</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>86</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2</v>
+        <v>20.8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>귀하의 직업은? (복수로 체크 가능)</t>
+          <t>귀하의직업은복수로체크가능</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="D14" t="n">
-        <v>9.699999999999999</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>귀하의 직업은? (복수로 체크 가능)</t>
+          <t>귀하의직업은복수로체크가능</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>5.6</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>귀하의 직업은? (복수로 체크 가능)</t>
+          <t>귀하의월소득수준은</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>85</v>
+        <v>182</v>
       </c>
       <c r="D16" t="n">
-        <v>20.5</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>귀하의 직업은? (복수로 체크 가능)</t>
+          <t>귀하의월소득수준은</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>78</v>
+        <v>161</v>
       </c>
       <c r="D17" t="n">
-        <v>18.8</v>
+        <v>38.9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>귀하의 직업은? (복수로 체크 가능)</t>
+          <t>귀하의월소득수준은</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="D18" t="n">
-        <v>10.6</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>귀하의 월소득 수준은?</t>
+          <t>귀하의월소득수준은</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>182</v>
+        <v>18</v>
       </c>
       <c r="D19" t="n">
-        <v>44</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>귀하의 월소득 수준은?</t>
+          <t>귀하가거주하는지역은</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="D20" t="n">
-        <v>38.9</v>
+        <v>43.7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>귀하의 월소득 수준은?</t>
+          <t>귀하가거주하는지역은</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>53</v>
+        <v>205</v>
       </c>
       <c r="D21" t="n">
-        <v>12.8</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>귀하의 월소득 수준은?</t>
+          <t>귀하가거주하는지역은</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="D22" t="n">
-        <v>4.3</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>귀하가 거주하는 지역은 ?</t>
+          <t>귀하의종교는</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -811,16 +811,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>181</v>
+        <v>401</v>
       </c>
       <c r="D23" t="n">
-        <v>43.7</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>귀하가 거주하는 지역은 ?</t>
+          <t>귀하의종교는</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -829,316 +829,154 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>205</v>
+        <v>13</v>
       </c>
       <c r="D24" t="n">
-        <v>49.5</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>귀하가 거주하는 지역은 ?</t>
+          <t>귀하의성경통독횟수는</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="D25" t="n">
-        <v>2.9</v>
+        <v>17.4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>귀하가 거주하는 지역은 ?</t>
+          <t>귀하의성경통독횟수는</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>3.9</v>
+        <v>16.4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>귀하의 종교는 ?</t>
+          <t>귀하의성경통독횟수는</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>401</v>
+        <v>274</v>
       </c>
       <c r="D27" t="n">
-        <v>96.90000000000001</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>귀하의 종교는 ?</t>
+          <t>귀하의교회직분은무엇입니까</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>185</v>
       </c>
       <c r="D28" t="n">
-        <v>0.7</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>귀하의 종교는 ?</t>
+          <t>귀하의교회직분은무엇입니까</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>167</v>
       </c>
       <c r="D29" t="n">
-        <v>0.5</v>
+        <v>40.3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>귀하의 종교는 ?</t>
+          <t>귀하의교회직분은무엇입니까</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="D30" t="n">
-        <v>1.9</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>귀하의 성경 통독 횟수는 ?</t>
+          <t>귀하의교회직분은무엇입니까</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>72</v>
+        <v>15</v>
       </c>
       <c r="D31" t="n">
-        <v>17.4</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>귀하의 성경 통독 횟수는 ?</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
-        <v>68</v>
+        <v>414</v>
       </c>
       <c r="D32" t="n">
-        <v>16.4</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
-        <is>
-          <t>귀하의 성경 통독 횟수는 ?</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>191</v>
-      </c>
-      <c r="D33" t="n">
-        <v>46.1</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>귀하의 성경 통독 횟수는 ?</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>83</v>
-      </c>
-      <c r="D34" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>귀하의 교회 직분은 무엇입니까?</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>185</v>
-      </c>
-      <c r="D35" t="n">
-        <v>44.7</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>귀하의 교회 직분은 무엇입니까?</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>167</v>
-      </c>
-      <c r="D36" t="n">
-        <v>40.3</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>귀하의 교회 직분은 무엇입니까?</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>47</v>
-      </c>
-      <c r="D37" t="n">
-        <v>11.4</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>귀하의 교회 직분은 무엇입니까?</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>15</v>
-      </c>
-      <c r="D38" t="n">
-        <v>3.6</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>성별</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>128</v>
-      </c>
-      <c r="D39" t="n">
-        <v>30.9</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>성별</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>286</v>
-      </c>
-      <c r="D40" t="n">
-        <v>69.09999999999999</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="n">
-        <v>414</v>
-      </c>
-      <c r="D41" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
         <is>
           <t>총 유효 표본(N) = 414명</t>
         </is>
